--- a/data/trans_bre/IP21-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 7,62</t>
+          <t>-5,74; 8,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -1,08</t>
+          <t>-13,52; -1,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 1,0</t>
+          <t>-12,38; 1,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 2,97</t>
+          <t>-5,19; 2,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,62; 379,57</t>
+          <t>-74,42; 362,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,85</t>
+          <t>-100,0; 103,17</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,49 +760,49 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 4,3</t>
+          <t>-4,74; 4,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 3,53</t>
+          <t>-5,82; 3,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 3,6</t>
+          <t>-3,36; 4,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,01</t>
+          <t>-2,8; 3,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,92; 184,24</t>
+          <t>-68,61; 166,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,0; 120,58</t>
+          <t>-73,51; 117,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,38; 546,41</t>
+          <t>-81,9; 512,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 745,48</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 6,78</t>
+          <t>-6,73; 6,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 4,11</t>
+          <t>-8,18; 3,48</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 2,98</t>
+          <t>-5,14; 3,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 6,48</t>
+          <t>-1,89; 6,87</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-74,34; 250,34</t>
+          <t>-70,85; 205,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-88,12; 166,75</t>
+          <t>-88,51; 160,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 2,69</t>
+          <t>-8,35; 2,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 1,59</t>
+          <t>-8,62; 1,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,78</t>
+          <t>-3,59; 5,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 3,04</t>
+          <t>-1,63; 2,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-88,5; 156,98</t>
+          <t>-91,45; 116,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 158,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 13,07</t>
+          <t>-1,27; 13,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 6,87</t>
+          <t>-8,7; 6,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 338,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 2,77</t>
+          <t>-7,57; 2,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 12,73</t>
+          <t>-0,48; 12,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 5,04</t>
+          <t>-5,72; 5,16</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 8,21</t>
+          <t>-1,86; 7,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 0,89</t>
+          <t>-6,99; 0,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 7,06</t>
+          <t>-0,88; 7,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 7,37</t>
+          <t>-0,2; 7,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,48; 0,71</t>
+          <t>-5,78; 0,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-88,65; 55,46</t>
+          <t>-90,23; 49,48</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-43,92; 353,03</t>
+          <t>-23,18; 409,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,64; 842,7</t>
+          <t>-17,23; 773,04</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 104,87</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,3; 1,13</t>
+          <t>-4,5; 1,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 2,12</t>
+          <t>-3,81; 2,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,69</t>
+          <t>-2,74; 2,58</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 0,0</t>
+          <t>-2,77; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-85,68; 82,59</t>
+          <t>-86,02; 99,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,88; 134,52</t>
+          <t>-77,11; 176,73</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,55; 260,06</t>
+          <t>-76,88; 267,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 0,96</t>
+          <t>-2,5; 0,82</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 1,27</t>
+          <t>-2,0; 1,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 1,72</t>
+          <t>-1,26; 1,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,8</t>
+          <t>-1,39; 0,81</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-44,93; 26,77</t>
+          <t>-46,74; 22,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,92; 34,49</t>
+          <t>-39,27; 35,48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,15; 81,72</t>
+          <t>-36,15; 77,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 80,43</t>
+          <t>-61,65; 76,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Provincia-trans_bre.xlsx
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,12</t>
+          <t>-6,06; 7,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,52; -1,24</t>
+          <t>-13,79; -1,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 1,32</t>
+          <t>-12,22; 1,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 2,64</t>
+          <t>-5,17; 2,84</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,42; 362,09</t>
+          <t>-74,46; 293,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 103,17</t>
+          <t>-100,0; 101,58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,7</t>
+          <t>-5,31; 4,36</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 3,46</t>
+          <t>-5,73; 3,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 4,02</t>
+          <t>-3,48; 3,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,08</t>
+          <t>-2,76; 3,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-68,61; 166,19</t>
+          <t>-70,88; 162,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,51; 117,83</t>
+          <t>-76,14; 111,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,9; 512,36</t>
+          <t>-81,59; 410,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 745,48</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -860,32 +860,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 6,84</t>
+          <t>-5,88; 6,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 3,48</t>
+          <t>-8,89; 3,88</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 3,01</t>
+          <t>-5,91; 2,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 6,87</t>
+          <t>-2,07; 7,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-70,85; 205,61</t>
+          <t>-70,61; 253,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-88,51; 160,9</t>
+          <t>-88,18; 164,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 2,46</t>
+          <t>-8,05; 1,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 1,36</t>
+          <t>-9,37; 1,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 5,25</t>
+          <t>-3,65; 5,16</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 2,46</t>
+          <t>-1,56; 2,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-91,45; 116,36</t>
+          <t>-89,11; 123,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 147,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 13,01</t>
+          <t>-0,01; 14,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 6,17</t>
+          <t>-8,6; 6,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 338,3</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,62</t>
+          <t>-7,52; 2,61</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 12,89</t>
+          <t>-0,14; 13,39</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 5,16</t>
+          <t>-5,39; 5,19</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,86; 7,91</t>
+          <t>-2,03; 8,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 0,56</t>
+          <t>-6,98; 1,01</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 7,33</t>
+          <t>-1,24; 7,48</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,11</t>
+          <t>-0,14; 7,03</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,78; 0,88</t>
+          <t>-5,49; 0,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-90,23; 49,48</t>
+          <t>-87,69; 76,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-23,18; 409,02</t>
+          <t>-33,57; 399,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 773,04</t>
+          <t>-26,43; 791,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 84,93</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 1,5</t>
+          <t>-4,51; 1,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,08</t>
+          <t>-3,68; 2,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 2,58</t>
+          <t>-2,45; 2,65</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-2,89; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-86,02; 99,67</t>
+          <t>-83,92; 111,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 176,73</t>
+          <t>-79,44; 144,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-76,88; 267,43</t>
+          <t>-72,45; 286,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 0,82</t>
+          <t>-2,65; 0,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 1,27</t>
+          <t>-2,2; 1,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,67</t>
+          <t>-1,07; 1,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,81</t>
+          <t>-1,36; 0,93</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-46,74; 22,96</t>
+          <t>-48,52; 24,44</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 35,48</t>
+          <t>-40,67; 34,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-36,15; 77,76</t>
+          <t>-31,76; 88,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-61,65; 76,95</t>
+          <t>-58,23; 94,66</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP21-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP21-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han estado ingresados en un hospital en los ultimos 12 meses</t>
+          <t>Menores que han estado ingresados/as en un hospital en los últimos 12 meses</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,55</t>
+          <t>-0,39</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-25,15%</t>
+          <t>-16,96%</t>
         </is>
       </c>
     </row>
@@ -660,27 +660,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 7,61</t>
+          <t>-5,61; 7,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,79; -1,32</t>
+          <t>-12,91; -1,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,22; 1,16</t>
+          <t>-12,17; 1,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 2,84</t>
+          <t>-4,64; 3,77</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-74,46; 293,47</t>
+          <t>-74,62; 379,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 101,58</t>
+          <t>-100,0; 82,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,08</t>
+          <t>0,72</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>46,81%</t>
         </is>
       </c>
     </row>
@@ -760,37 +760,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 4,36</t>
+          <t>-4,55; 4,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 3,47</t>
+          <t>-6,31; 3,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,67</t>
+          <t>-3,62; 3,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,19</t>
+          <t>-2,25; 4,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-70,88; 162,94</t>
+          <t>-68,92; 184,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-76,14; 111,58</t>
+          <t>-77,0; 120,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,59; 410,04</t>
+          <t>-81,38; 546,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,66</t>
+          <t>1,86</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>101,33%</t>
+          <t>121,53%</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 6,76</t>
+          <t>-6,68; 6,78</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,89; 3,88</t>
+          <t>-7,9; 4,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -875,17 +875,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 7,34</t>
+          <t>-1,55; 7,5</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-70,61; 253,01</t>
+          <t>-74,34; 250,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-88,18; 164,09</t>
+          <t>-88,12; 166,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>0,1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 1,84</t>
+          <t>-8,43; 2,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 1,56</t>
+          <t>-9,76; 1,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 5,16</t>
+          <t>-3,34; 5,78</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 2,51</t>
+          <t>-1,33; 2,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-89,11; 123,17</t>
+          <t>-88,5; 156,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 147,97</t>
+          <t>-100,0; 158,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1060,12 +1060,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 14,46</t>
+          <t>-0,08; 13,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,6; 6,96</t>
+          <t>-8,68; 6,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>1,66</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>109,22%</t>
+          <t>107,98%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 2,61</t>
+          <t>-7,88; 2,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 13,39</t>
+          <t>-0,56; 12,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 5,19</t>
+          <t>-5,24; 5,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 8,3</t>
+          <t>-1,78; 7,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>-2,06</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-56,43%</t>
+          <t>-61,28%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; 1,01</t>
+          <t>-6,74; 0,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 7,48</t>
+          <t>-1,85; 7,06</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 7,03</t>
+          <t>-0,05; 7,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 0,89</t>
+          <t>-6,25; 0,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-87,69; 76,96</t>
+          <t>-88,65; 55,46</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-33,57; 399,13</t>
+          <t>-43,92; 353,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 791,52</t>
+          <t>-21,64; 842,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 84,93</t>
+          <t>-100,0; 92,12</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,77</t>
+          <t>-0,75</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,67</t>
+          <t>-4,3; 1,13</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,14</t>
+          <t>-3,56; 2,12</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 2,65</t>
+          <t>-2,52; 2,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,0</t>
+          <t>-3,31; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,92; 111,45</t>
+          <t>-85,68; 82,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-79,44; 144,44</t>
+          <t>-79,88; 134,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-72,45; 286,82</t>
+          <t>-76,55; 260,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-0,21</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-15,26%</t>
+          <t>-13,0%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 0,9</t>
+          <t>-2,4; 0,96</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 1,21</t>
+          <t>-2,1; 1,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 1,73</t>
+          <t>-1,09; 1,72</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,93</t>
+          <t>-1,28; 0,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-48,52; 24,44</t>
+          <t>-44,93; 26,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-40,67; 34,56</t>
+          <t>-40,92; 34,49</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 88,49</t>
+          <t>-31,15; 81,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 94,66</t>
+          <t>-59,93; 85,08</t>
         </is>
       </c>
     </row>
